--- a/20250815_dataset_guide_MM_V1.xlsx
+++ b/20250815_dataset_guide_MM_V1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\marshall_group\User\gp1mmx\housing_populism\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2316B685-0756-4436-81B7-DDF7FD32AF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77CF363-D218-4B19-B398-20A464525C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5FF58C6B-ED44-4846-AD90-2C48070ED693}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>Dataset</t>
   </si>
@@ -278,18 +278,6 @@
     <t>y</t>
   </si>
   <si>
-    <t>Residential turnover</t>
-  </si>
-  <si>
-    <t>hh_churn_oslaua_2023</t>
-  </si>
-  <si>
-    <t>1997-2022</t>
-  </si>
-  <si>
-    <t>https://data.geods.ac.uk/dataset/residential-mobility-index</t>
-  </si>
-  <si>
     <t>British election survey W22</t>
   </si>
   <si>
@@ -311,22 +299,19 @@
     <t>https://www.britishelectionstudy.com/data-objects/panel-study-data/</t>
   </si>
   <si>
-    <t>Landlord possession claims</t>
-  </si>
-  <si>
-    <t>possession_statistics_2024</t>
-  </si>
-  <si>
-    <t>MAP_CSV</t>
-  </si>
-  <si>
-    <t>https://assets.publishing.service.gov.uk/media/66b360d9a3c2a28abb50de35/Mortgage_and_landlord_statistical_data.zip</t>
-  </si>
-  <si>
-    <t>https://assets.publishing.service.gov.uk/media/620397bce90e077f71cd545b/Mortgage_and_landlord_statistical_data.zip</t>
-  </si>
-  <si>
-    <t>possession_statistics_2021</t>
+    <t>https://www.ons.gov.uk/file?uri=/economy/inflationandpriceindices/datasets/priceindexofprivaterentsukmonthlypricestatistics/21january2026/priceindexofprivaterentsukmonthlypricestatistics.xlsx</t>
+  </si>
+  <si>
+    <t>2015-2025</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>priceindexofprivaterentsukmonthlypricestatistics</t>
+  </si>
+  <si>
+    <t>Rental price</t>
   </si>
 </sst>
 </file>
@@ -1248,33 +1233,33 @@
         <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F24" s="1">
-        <v>45897</v>
+        <v>46057</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
         <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
       </c>
       <c r="E25" s="2">
         <v>2021</v>
@@ -1283,18 +1268,18 @@
         <v>45901</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2">
         <v>2024</v>
@@ -1303,54 +1288,14 @@
         <v>45901</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F27" s="1">
-        <v>45902</v>
-      </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
+      <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F28" s="1">
-        <v>45902</v>
-      </c>
-      <c r="G28" t="s">
-        <v>95</v>
-      </c>
+      <c r="F28" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G21">

--- a/20250815_dataset_guide_MM_V1.xlsx
+++ b/20250815_dataset_guide_MM_V1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\marshall_group\User\gp1mmx\housing_populism\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77CF363-D218-4B19-B398-20A464525C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A02664-CDBE-47F1-B752-FE480FCCF990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5FF58C6B-ED44-4846-AD90-2C48070ED693}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
   <si>
     <t>Dataset</t>
   </si>
@@ -270,12 +270,6 @@
   </si>
   <si>
     <t>2021 &amp; 2024</t>
-  </si>
-  <si>
-    <t>csv</t>
-  </si>
-  <si>
-    <t>y</t>
   </si>
   <si>
     <t>British election survey W22</t>
@@ -688,619 +682,547 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6046FEFF-7B6C-4C9D-8A89-917581189BF4}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2024</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E6" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E7" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E10" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2021</v>
+      </c>
+      <c r="E21" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="1">
+        <v>45884</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="1">
+        <v>46057</v>
+      </c>
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F2" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="2">
         <v>2021</v>
       </c>
-      <c r="F6" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F7" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F8" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F10" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F21" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="1">
-        <v>45884</v>
-      </c>
-      <c r="G23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+      <c r="E25" s="1">
+        <v>45230</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F25" s="1">
-        <v>45901</v>
-      </c>
-      <c r="G25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>82</v>
       </c>
       <c r="C26" t="s">
         <v>83</v>
       </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="D26" s="2">
         <v>2024</v>
       </c>
-      <c r="F26" s="1">
+      <c r="E26" s="1">
         <v>45901</v>
       </c>
-      <c r="G26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F28" s="1"/>
+      <c r="F26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E28" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G21">
-    <sortCondition ref="B2:B21"/>
-    <sortCondition ref="E2:E21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+    <sortCondition ref="A2:A21"/>
+    <sortCondition ref="D2:D21"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
